--- a/Rodovias/modelos_rodovias/doutor_manoel_hyppolito_rego_km_83_caraguatatuba_sp_rf_regimes/importancias.xlsx
+++ b/Rodovias/modelos_rodovias/doutor_manoel_hyppolito_rego_km_83_caraguatatuba_sp_rf_regimes/importancias.xlsx
@@ -435,27 +435,27 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04674136800094384</v>
+        <v>0.04801537257699898</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>interacao_meta_umidade</t>
+          <t>interacao_meta_temperatura</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04081937518589956</v>
+        <v>0.0421888996868643</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>interacao_meta_temperatura</t>
+          <t>interacao_meta_umidade</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0398175544941969</v>
+        <v>0.0416287783943964</v>
       </c>
     </row>
     <row r="5">
@@ -465,37 +465,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0277825258318849</v>
+        <v>0.02943027077284584</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>meta_std_12</t>
+          <t>interacao_meta_hora_cos</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02650410262376758</v>
+        <v>0.02661753117020146</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>meta_lag_6</t>
+          <t>meta_std_12</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02626717618143503</v>
+        <v>0.02649377159283036</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>interacao_meta_hora_cos</t>
+          <t>minuto</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02606364603010446</v>
+        <v>0.0253330735518983</v>
       </c>
     </row>
     <row r="9">
@@ -505,57 +505,57 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02542666854865429</v>
+        <v>0.02484323801769953</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>minuto</t>
+          <t>meta_delta_media_12</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02504028324940577</v>
+        <v>0.02472275035696472</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>meta_delta_media_12</t>
+          <t>meta_lag_6</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02480131046732898</v>
+        <v>0.02437922778195628</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>meta_std_6</t>
+          <t>meta_media_6</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02395237695125804</v>
+        <v>0.02365943677801318</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>hora_decimal</t>
+          <t>meta_std_6</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02299026571016724</v>
+        <v>0.02351142255529994</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>meta_std_4</t>
+          <t>meta_delta_4</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02289393700046536</v>
+        <v>0.0231864077333309</v>
       </c>
     </row>
     <row r="15">
@@ -565,17 +565,17 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02281508688269908</v>
+        <v>0.02301074579094633</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>meta_media_6</t>
+          <t>hora_decimal</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02280849522701517</v>
+        <v>0.02275781762294771</v>
       </c>
     </row>
     <row r="17">
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.02280566481758065</v>
+        <v>0.02220114242214529</v>
       </c>
     </row>
     <row r="18">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.02255587554512162</v>
+        <v>0.02219212358051655</v>
       </c>
     </row>
     <row r="19">
@@ -605,77 +605,77 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.02245099940745388</v>
+        <v>0.02214005331758989</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>meta_media_3</t>
+          <t>meta_std_4</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.02232260018349983</v>
+        <v>0.02207707082856957</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>meta_lag_2</t>
+          <t>meta_media_12</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.02224812582433939</v>
+        <v>0.02187226680636863</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>meta_delta_4</t>
+          <t>meta_lag_4</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02215666595433335</v>
+        <v>0.02182776784547429</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>meta_delta_1</t>
+          <t>meta_media_4</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.02210566622777</v>
+        <v>0.02168623920784047</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>meta_lag_4</t>
+          <t>meta_delta_1</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.02188234761175587</v>
+        <v>0.02164401878607889</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>meta_media_4</t>
+          <t>meta_media_3</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.02174821431568313</v>
+        <v>0.02159174474982122</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>meta_media_12</t>
+          <t>meta_lag_2</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.02167262621693955</v>
+        <v>0.02134706695308245</v>
       </c>
     </row>
     <row r="27">
@@ -685,27 +685,27 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.02082539409146239</v>
+        <v>0.02052376146668761</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>meta_delta_2</t>
+          <t>meta_lag_3</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.02056224714645097</v>
+        <v>0.02048712542897866</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>meta_lag_3</t>
+          <t>meta_delta_2</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.01979028602608185</v>
+        <v>0.02037577188937829</v>
       </c>
     </row>
     <row r="30">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.01870929853664163</v>
+        <v>0.01917458251532966</v>
       </c>
     </row>
     <row r="31">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.01726105358981749</v>
+        <v>0.01683355340865876</v>
       </c>
     </row>
     <row r="32">
@@ -735,37 +735,37 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.01596566816940565</v>
+        <v>0.01664736740004191</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cobertura_nuvens</t>
+          <t>temperatura_2m</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.01555404696893156</v>
+        <v>0.01547687000030032</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>temperatura_2m</t>
+          <t>umidade_relativa</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.01549093270785637</v>
+        <v>0.01540800296513614</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>umidade_relativa</t>
+          <t>cobertura_nuvens</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.01538863057144457</v>
+        <v>0.01512928562564311</v>
       </c>
     </row>
     <row r="36">
@@ -775,37 +775,37 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.01427910848090961</v>
+        <v>0.01400650771177698</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>soma_alvo_12</t>
+          <t>media_alvo_12</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.01009019024592922</v>
+        <v>0.01028807948746135</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>tendencia_curta_1_3</t>
+          <t>soma_alvo_12</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.009785628393193767</v>
+        <v>0.009654790899850127</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>media_alvo_12</t>
+          <t>tendencia_curta_1_3</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.009679237696086938</v>
+        <v>0.009597863744235028</v>
       </c>
     </row>
     <row r="40">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.008693258373890523</v>
+        <v>0.00884858820196972</v>
       </c>
     </row>
     <row r="41">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.008426419461957249</v>
+        <v>0.008308043979859802</v>
       </c>
     </row>
     <row r="42">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.00824296770914853</v>
+        <v>0.007815602258177805</v>
       </c>
     </row>
     <row r="43">
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.00792228329176327</v>
+        <v>0.007704183218763354</v>
       </c>
     </row>
     <row r="44">
@@ -855,97 +855,97 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.00756728541007136</v>
+        <v>0.007645577151574755</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>soma_alvo_6</t>
+          <t>media_alvo_6</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.007471271142298909</v>
+        <v>0.007115770151648858</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>media_alvo_6</t>
+          <t>soma_alvo_6</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.007031269845366967</v>
+        <v>0.006544382522907472</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>chuva_mm</t>
+          <t>media_alvo_3</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.006821576430034352</v>
+        <v>0.006355579526305249</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>media_alvo_3</t>
+          <t>chuva_mm</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.006205498092091227</v>
+        <v>0.006236596649097387</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>hora_cos</t>
+          <t>soma_alvo_3</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.005976196710876844</v>
+        <v>0.006091529220552683</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>soma_alvo_3</t>
+          <t>dia_semana_cos</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.005903618848464587</v>
+        <v>0.005844100398721224</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>dia_semana_cos</t>
+          <t>hora_cos</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.005704385776329061</v>
+        <v>0.005756228424157934</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>alvo_lag_1</t>
+          <t>tendencia_curta_1_2</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.005695190156695933</v>
+        <v>0.005268079978753521</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>tendencia_curta_1_2</t>
+          <t>alvo_lag_1</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.005548593053265429</v>
+        <v>0.004632381454243642</v>
       </c>
     </row>
     <row r="54">
@@ -955,27 +955,27 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.004225668325485182</v>
+        <v>0.004305846083144169</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>alvo_lag_2</t>
+          <t>cluster_regime</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.004111569918831307</v>
+        <v>0.004286096336256273</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>alvo_lag_12</t>
+          <t>alvo_lag_2</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.003976998744811972</v>
+        <v>0.004069657992749542</v>
       </c>
     </row>
     <row r="57">
@@ -985,37 +985,37 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.00339596386685045</v>
+        <v>0.003389387942642859</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>alvo_lag_6</t>
+          <t>alvo_lag_12</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.003351391851969651</v>
+        <v>0.003317811562893098</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>alvo_lag_4</t>
+          <t>alvo_lag_6</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.002973921634747402</v>
+        <v>0.00317712652806498</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>cluster_regime</t>
+          <t>alvo_lag_4</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.00292593447983747</v>
+        <v>0.003055516311836955</v>
       </c>
     </row>
     <row r="61">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.002436848275027784</v>
+        <v>0.002545666291531985</v>
       </c>
     </row>
     <row r="62">
@@ -1035,147 +1035,147 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.001813473491555073</v>
+        <v>0.001924373345542753</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>estava_chovendo</t>
+          <t>cluster_regime_2</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.001658357680482795</v>
+        <v>0.001764955745222828</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>eh_dia_util</t>
+          <t>eh_pico_tarde</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.001628277636357689</v>
+        <v>0.001713061841754362</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>bloco_manha</t>
+          <t>estava_chovendo</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.001608140931524448</v>
+        <v>0.001618202250693212</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>cluster_regime_0</t>
+          <t>fim_semana</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.00159830453204152</v>
+        <v>0.001601278767736058</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>bloco_almoco</t>
+          <t>bloco_manha</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.001536329799020624</v>
+        <v>0.001536049539165203</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>cluster_regime_2</t>
+          <t>eh_dia_util</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.001528141749224327</v>
+        <v>0.00149974755194178</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>eh_pico_tarde</t>
+          <t>eh_sabado</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.001512888840351901</v>
+        <v>0.001410793676272919</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>eh_sabado</t>
+          <t>cluster_regime_0</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.0014418303128161</v>
+        <v>0.00140416642327099</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>fim_semana</t>
+          <t>bloco_almoco</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.001392391699878529</v>
+        <v>0.001396300736289836</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>cluster_regime_1</t>
+          <t>bloco_tarde_pico</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.001358257326133285</v>
+        <v>0.001357262839697589</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>bloco_tarde_pico</t>
+          <t>cluster_regime_3</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.001254013796537368</v>
+        <v>0.001268966536605782</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>eh_domingo</t>
+          <t>cluster_regime_1</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.001060905283531476</v>
+        <v>0.001152317007838824</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>cluster_regime_3</t>
+          <t>eh_pico_manha</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.001060178577259018</v>
+        <v>0.00113952606449362</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>eh_pico_manha</t>
+          <t>eh_domingo</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.001041528732711937</v>
+        <v>0.001057731980265158</v>
       </c>
     </row>
     <row r="77">
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.0009360166253947014</v>
+        <v>0.0009435173893646957</v>
       </c>
     </row>
     <row r="78">
@@ -1195,27 +1195,27 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.0008415417200649051</v>
+        <v>0.0008745347253657268</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>mes_sin</t>
+          <t>mes</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.0008290369236516847</v>
+        <v>0.0008504635104018122</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>mes</t>
+          <t>mes_sin</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.0007170849721666352</v>
+        <v>0.0008496219414869814</v>
       </c>
     </row>
     <row r="81">
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.0005205068555649552</v>
+        <v>0.0003615745165772305</v>
       </c>
     </row>
   </sheetData>

--- a/Rodovias/modelos_rodovias/doutor_manoel_hyppolito_rego_km_83_caraguatatuba_sp_rf_regimes/importancias.xlsx
+++ b/Rodovias/modelos_rodovias/doutor_manoel_hyppolito_rego_km_83_caraguatatuba_sp_rf_regimes/importancias.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,7 +435,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04801537257699898</v>
+        <v>0.09829358085180215</v>
       </c>
     </row>
     <row r="3">
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0421888996868643</v>
+        <v>0.09448755956690379</v>
       </c>
     </row>
     <row r="4">
@@ -455,777 +455,347 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0416287783943964</v>
+        <v>0.09228907840792358</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>interacao_meta_hora_sin</t>
+          <t>interacao_meta_hora_cos</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02943027077284584</v>
+        <v>0.08498211063531623</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>interacao_meta_hora_cos</t>
+          <t>interacao_meta_hora_sin</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02661753117020146</v>
+        <v>0.08104446602590142</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>meta_std_12</t>
+          <t>minuto</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02649377159283036</v>
+        <v>0.07655497001564021</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>minuto</t>
+          <t>hora_decimal</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0253330735518983</v>
+        <v>0.06546405409704271</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>tendencia_curta_meta</t>
+          <t>hora_sin</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02484323801769953</v>
+        <v>0.06464564270105029</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>meta_delta_media_12</t>
+          <t>hora_cos</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02472275035696472</v>
+        <v>0.06223985705573378</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>meta_lag_6</t>
+          <t>temperatura_2m</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02437922778195628</v>
+        <v>0.04553602950644316</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>meta_media_6</t>
+          <t>umidade_relativa</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02365943677801318</v>
+        <v>0.04481199826683947</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>meta_std_6</t>
+          <t>cobertura_nuvens</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02351142255529994</v>
+        <v>0.04328400644212667</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>meta_delta_4</t>
+          <t>dia_semana_sin</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0231864077333309</v>
+        <v>0.02546418942697824</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>meta_delta_media_4</t>
+          <t>dia_semana</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02301074579094633</v>
+        <v>0.02221255917969205</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>hora_decimal</t>
+          <t>hora</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02275781762294771</v>
+        <v>0.01731402808847468</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>meta_std_3</t>
+          <t>dia_semana_cos</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.02220114242214529</v>
+        <v>0.01475276748651875</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>meta_lag_12</t>
+          <t>chuva_mm</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.02219212358051655</v>
+        <v>0.01342335828778472</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tendencia_media_meta</t>
+          <t>bloco_dia_cod</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.02214005331758989</v>
+        <v>0.006256575372993039</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>meta_std_4</t>
+          <t>eh_sexta</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.02207707082856957</v>
+        <v>0.00619208965720662</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>meta_media_12</t>
+          <t>estava_chovendo</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.02187226680636863</v>
+        <v>0.004536049025572631</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>meta_lag_4</t>
+          <t>eh_dia_util</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02182776784547429</v>
+        <v>0.004286935478496083</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>meta_media_4</t>
+          <t>fim_semana</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.02168623920784047</v>
+        <v>0.003930399737755038</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>meta_delta_1</t>
+          <t>eh_sabado</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.02164401878607889</v>
+        <v>0.003748621173985256</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>meta_media_3</t>
+          <t>bloco_manha</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.02159174474982122</v>
+        <v>0.003576445515269794</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>meta_lag_2</t>
+          <t>eh_domingo</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.02134706695308245</v>
+        <v>0.003265898433676692</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>meta_lag_1</t>
+          <t>bloco_almoco</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.02052376146668761</v>
+        <v>0.003030975681744054</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>meta_lag_3</t>
+          <t>eh_pico_tarde</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.02048712542897866</v>
+        <v>0.002443489869397214</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>meta_delta_2</t>
+          <t>bloco_tarde_pico</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.02037577188937829</v>
+        <v>0.002399421383950762</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>meta_max_4</t>
+          <t>eh_pico_manha</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.01917458251532966</v>
+        <v>0.002202364045053316</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>meta_min_4</t>
+          <t>mes_cos</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.01683355340865876</v>
+        <v>0.001816951628267528</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>meta_max_12</t>
+          <t>bloco_pico_manha</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.01664736740004191</v>
+        <v>0.001757048121337187</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>temperatura_2m</t>
+          <t>mes_sin</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.01547687000030032</v>
+        <v>0.001652921853221685</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>umidade_relativa</t>
+          <t>mes</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.01540800296513614</v>
+        <v>0.001652355049690936</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cobertura_nuvens</t>
+          <t>bloco_noite</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.01512928562564311</v>
+        <v>0.0004512019302102771</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>meta_min_12</t>
+          <t>bloco_madrugada</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.01400650771177698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>media_alvo_12</t>
+          <t>bloco_outro</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.01028807948746135</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>soma_alvo_12</t>
+          <t>bloco_late_night</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.009654790899850127</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>tendencia_curta_1_3</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>0.009597863744235028</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>hora_sin</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>0.00884858820196972</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>hora</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>0.008308043979859802</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>dia_semana</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>0.007815602258177805</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>dia_semana_sin</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>0.007704183218763354</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>tendencia_curta_1_6</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>0.007645577151574755</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>media_alvo_6</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>0.007115770151648858</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>soma_alvo_6</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>0.006544382522907472</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>media_alvo_3</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>0.006355579526305249</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>chuva_mm</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>0.006236596649097387</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>soma_alvo_3</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>0.006091529220552683</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>dia_semana_cos</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>0.005844100398721224</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>hora_cos</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>0.005756228424157934</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>tendencia_curta_1_2</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>0.005268079978753521</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>alvo_lag_1</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>0.004632381454243642</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>alvo_lag_3</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>0.004305846083144169</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>cluster_regime</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>0.004286096336256273</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>alvo_lag_2</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>0.004069657992749542</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>bloco_dia_cod</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>0.003389387942642859</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>alvo_lag_12</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>0.003317811562893098</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>alvo_lag_6</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>0.00317712652806498</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>alvo_lag_4</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>0.003055516311836955</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>acelerando_meta</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>0.002545666291531985</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>eh_sexta</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>0.001924373345542753</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>cluster_regime_2</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>0.001764955745222828</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>eh_pico_tarde</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>0.001713061841754362</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>estava_chovendo</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>0.001618202250693212</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>fim_semana</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>0.001601278767736058</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>bloco_manha</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>0.001536049539165203</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>eh_dia_util</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>0.00149974755194178</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>eh_sabado</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>0.001410793676272919</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>cluster_regime_0</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>0.00140416642327099</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>bloco_almoco</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>0.001396300736289836</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>bloco_tarde_pico</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>0.001357262839697589</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>cluster_regime_3</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>0.001268966536605782</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>cluster_regime_1</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>0.001152317007838824</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>eh_pico_manha</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>0.00113952606449362</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>eh_domingo</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>0.001057731980265158</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>mes_cos</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>0.0009435173893646957</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>bloco_pico_manha</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>0.0008745347253657268</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>mes</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>0.0008504635104018122</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>mes_sin</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>0.0008496219414869814</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>bloco_noite</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>0.0003615745165772305</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Rodovias/modelos_rodovias/doutor_manoel_hyppolito_rego_km_83_caraguatatuba_sp_rf_regimes/importancias.xlsx
+++ b/Rodovias/modelos_rodovias/doutor_manoel_hyppolito_rego_km_83_caraguatatuba_sp_rf_regimes/importancias.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,370 +431,470 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>meta_num</t>
+          <t>roll5_ratio_pass_total_meta</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.09829358085180215</v>
+        <v>0.07478174828331491</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>interacao_meta_temperatura</t>
+          <t>roll3_ratio_pass_total_meta</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09448755956690379</v>
+        <v>0.06877069125199312</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>interacao_meta_umidade</t>
+          <t>meta_num</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09228907840792358</v>
+        <v>0.0523131147480474</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>interacao_meta_hora_cos</t>
+          <t>interacao_meta_umidade</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08498211063531623</v>
+        <v>0.05001052203140716</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>interacao_meta_hora_sin</t>
+          <t>interacao_meta_temperatura</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08104446602590142</v>
+        <v>0.04953845918597775</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>minuto</t>
+          <t>lag1_ratio_pass_total_meta</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07655497001564021</v>
+        <v>0.04454521510561107</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>hora_decimal</t>
+          <t>minuto</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06546405409704271</v>
+        <v>0.04318562445092283</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>hora_sin</t>
+          <t>lag1_pass_total_mercado</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.06464564270105029</v>
+        <v>0.04252582867774504</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>hora_cos</t>
+          <t>interacao_meta_hora_sin</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.06223985705573378</v>
+        <v>0.04180752741765491</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>temperatura_2m</t>
+          <t>roll10_mean_pass_total_mercado</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.04553602950644316</v>
+        <v>0.04142976384251271</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>umidade_relativa</t>
+          <t>lag1_pass_tendencia_5m</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04481199826683947</v>
+        <v>0.04111567860631542</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cobertura_nuvens</t>
+          <t>roll3_mean_pass_total_mercado</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04328400644212667</v>
+        <v>0.04067060922020103</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>dia_semana_sin</t>
+          <t>interacao_meta_hora_cos</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02546418942697824</v>
+        <v>0.04018799808175542</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>dia_semana</t>
+          <t>roll5_mean_pass_total_mercado</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02221255917969205</v>
+        <v>0.03933008363604673</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>hora</t>
+          <t>hora_decimal</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01731402808847468</v>
+        <v>0.03453449876612519</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>dia_semana_cos</t>
+          <t>hora_sin</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.01475276748651875</v>
+        <v>0.03439347685767766</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>chuva_mm</t>
+          <t>hora_cos</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.01342335828778472</v>
+        <v>0.03388183668659462</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bloco_dia_cod</t>
+          <t>lag1_pass_qtd_ultimos_2min</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.006256575372993039</v>
+        <v>0.03029789867542981</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>eh_sexta</t>
+          <t>lag1_pass_media_ultimos_2min</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.00619208965720662</v>
+        <v>0.02978521010371921</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>estava_chovendo</t>
+          <t>temperatura_2m</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.004536049025572631</v>
+        <v>0.02660508470769219</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>eh_dia_util</t>
+          <t>umidade_relativa</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.004286935478496083</v>
+        <v>0.02516139938927648</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>fim_semana</t>
+          <t>cobertura_nuvens</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.003930399737755038</v>
+        <v>0.02483643518637903</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>eh_sabado</t>
+          <t>dia_semana</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.003748621173985256</v>
+        <v>0.01379007333120661</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>bloco_manha</t>
+          <t>hora</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.003576445515269794</v>
+        <v>0.01285961639629494</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>eh_domingo</t>
+          <t>dia_semana_sin</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.003265898433676692</v>
+        <v>0.01249017595868819</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bloco_almoco</t>
+          <t>dia_semana_cos</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.003030975681744054</v>
+        <v>0.00930675911970026</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>eh_pico_tarde</t>
+          <t>chuva_mm</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.002443489869397214</v>
+        <v>0.008104353339286807</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>bloco_tarde_pico</t>
+          <t>bloco_dia_cod</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.002399421383950762</v>
+        <v>0.004942324866135829</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>eh_pico_manha</t>
+          <t>bloco_manha</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.002202364045053316</v>
+        <v>0.003075498442985815</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>mes_cos</t>
+          <t>eh_sexta</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.001816951628267528</v>
+        <v>0.002890536201874449</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bloco_pico_manha</t>
+          <t>estava_chovendo</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.001757048121337187</v>
+        <v>0.002559368965892924</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>mes_sin</t>
+          <t>bloco_almoco</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.001652921853221685</v>
+        <v>0.002513225363622032</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>mes</t>
+          <t>eh_pico_tarde</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.001652355049690936</v>
+        <v>0.002378580882357496</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bloco_noite</t>
+          <t>eh_sabado</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.0004512019302102771</v>
+        <v>0.002241609093000196</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bloco_madrugada</t>
+          <t>eh_dia_util</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>0.002141461618254904</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bloco_outro</t>
+          <t>fim_semana</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>0.002053899892863</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>bloco_tarde_pico</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.001661823422085115</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>eh_pico_manha</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.001606671732546347</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>eh_domingo</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.001274064344998207</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>bloco_pico_manha</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.001135849222020959</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>mes_cos</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0.001043671129022276</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>mes_sin</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.0009958900896594374</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>mes</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0.0009252627723412648</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>bloco_noite</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0.000300578902763317</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>bloco_madrugada</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>bloco_outro</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>bloco_late_night</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B48" t="n">
         <v>0</v>
       </c>
     </row>
